--- a/data/Blumenau/Junho 2026 - Super A.xlsx
+++ b/data/Blumenau/Junho 2026 - Super A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://furb-my.sharepoint.com/personal/bttomio_furb_br/Documents/Economia na Prática/2026.1/Coleta de preços em supermercados/Blumenau/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bttomio\Documents\GitHub\CidadaniaFinanceira\data\Blumenau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E71BCE53-622C-4F03-8C16-E373BE27074D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF56C4E3-103E-42E5-9A28-97E645A0F4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="56">
   <si>
     <t>MERCADO</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Caravelas</t>
   </si>
   <si>
-    <t>Cana Real</t>
-  </si>
-  <si>
     <t>Café em pó</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>Tirol</t>
   </si>
   <si>
-    <t>President</t>
-  </si>
-  <si>
     <t>Batavo</t>
   </si>
   <si>
@@ -182,12 +176,6 @@
     <t>Granel</t>
   </si>
   <si>
-    <t>Patinho</t>
-  </si>
-  <si>
-    <t>Coxão mole</t>
-  </si>
-  <si>
     <t>Coxão duro</t>
   </si>
   <si>
@@ -210,9 +198,6 @@
   </si>
   <si>
     <t>Parmalat</t>
-  </si>
-  <si>
-    <t>Piracanjuba</t>
   </si>
   <si>
     <t>Banana</t>
@@ -764,6 +749,75 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -781,75 +835,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,18 +1232,18 @@
       <c r="A5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="57"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="16"/>
       <c r="I5" s="17"/>
       <c r="J5" s="5"/>
@@ -1280,12 +1265,12 @@
       <c r="D6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="20" t="s">
         <v>9</v>
       </c>
@@ -1296,16 +1281,16 @@
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="40">
         <v>1</v>
       </c>
       <c r="E7" s="21" t="s">
@@ -1320,7 +1305,7 @@
       <c r="H7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="42">
         <f>AVERAGE(F8:H8)</f>
         <v>2.7833333333333332</v>
       </c>
@@ -1331,10 +1316,10 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="53"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="24" t="s">
         <v>17</v>
       </c>
@@ -1347,7 +1332,7 @@
       <c r="H8" s="25">
         <v>3.18</v>
       </c>
-      <c r="I8" s="39"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -1355,16 +1340,16 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="48">
         <v>1</v>
       </c>
       <c r="E9" s="26" t="s">
@@ -1376,12 +1361,10 @@
       <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="46">
+      <c r="H9" s="28"/>
+      <c r="I9" s="50">
         <f>AVERAGE(F10:H10)</f>
-        <v>7.9766666666666666</v>
+        <v>3.67</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1390,10 +1373,10 @@
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56"/>
+      <c r="A10" s="45"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="49"/>
       <c r="E10" s="29" t="s">
         <v>17</v>
       </c>
@@ -1403,10 +1386,8 @@
       <c r="G10" s="30">
         <v>3.95</v>
       </c>
-      <c r="H10" s="30">
-        <v>16.59</v>
-      </c>
-      <c r="I10" s="47"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="51"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -1414,31 +1395,31 @@
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="50" t="s">
+      <c r="A11" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="40">
         <v>0.5</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="H11" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="38">
+      <c r="I11" s="42">
         <f>AVERAGE(F12:H12)</f>
         <v>22.49</v>
       </c>
@@ -1449,10 +1430,10 @@
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="49"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="53"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="24" t="s">
         <v>17</v>
       </c>
@@ -1465,7 +1446,7 @@
       <c r="H12" s="25">
         <v>16.98</v>
       </c>
-      <c r="I12" s="39"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -1473,31 +1454,31 @@
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="48">
+        <v>1</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="44">
-        <v>1</v>
-      </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="G13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="H13" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="46">
+      <c r="I13" s="50">
         <f>AVERAGE(F14:H14)</f>
         <v>3.0960000000000001</v>
       </c>
@@ -1508,10 +1489,10 @@
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="54"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="49"/>
       <c r="E14" s="29" t="s">
         <v>17</v>
       </c>
@@ -1524,7 +1505,7 @@
       <c r="H14" s="30">
         <v>3.39</v>
       </c>
-      <c r="I14" s="47"/>
+      <c r="I14" s="51"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -1532,31 +1513,31 @@
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="50" t="s">
+      <c r="A15" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="40">
         <v>1</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="H15" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="38">
+      <c r="I15" s="42">
         <f>AVERAGE(F16:H16)</f>
         <v>4.59</v>
       </c>
@@ -1567,10 +1548,10 @@
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="53"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="24" t="s">
         <v>17</v>
       </c>
@@ -1583,7 +1564,7 @@
       <c r="H16" s="25">
         <v>5.39</v>
       </c>
-      <c r="I16" s="39"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -1591,33 +1572,31 @@
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="48">
         <v>0.5</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="46">
+      <c r="I17" s="50">
         <f>AVERAGE(F18:H18)</f>
-        <v>30.201666666666668</v>
+        <v>28.189999999999998</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -1626,23 +1605,21 @@
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="29" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="30">
         <v>25.99</v>
       </c>
-      <c r="G18" s="30">
-        <v>34.225000000000001</v>
-      </c>
+      <c r="G18" s="30"/>
       <c r="H18" s="30">
         <v>30.39</v>
       </c>
-      <c r="I18" s="47"/>
+      <c r="I18" s="51"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -1650,31 +1627,31 @@
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="52">
+      <c r="D19" s="40">
         <v>0.9</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="38">
+      <c r="I19" s="42">
         <f>AVERAGE(F20:H20)</f>
         <v>7.8566666666666665</v>
       </c>
@@ -1685,10 +1662,10 @@
       <c r="N19" s="5"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="53"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="24" t="s">
         <v>17</v>
       </c>
@@ -1701,7 +1678,7 @@
       <c r="H20" s="25">
         <v>8.19</v>
       </c>
-      <c r="I20" s="39"/>
+      <c r="I20" s="43"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -1709,33 +1686,29 @@
       <c r="N20" s="5"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="42" t="s">
+      <c r="A21" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="48">
         <v>1</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>49</v>
-      </c>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="46">
+        <v>46</v>
+      </c>
+      <c r="I21" s="50">
         <f>AVERAGE(F22:H22)</f>
-        <v>51.129999999999995</v>
+        <v>47.59</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -1744,23 +1717,19 @@
       <c r="N21" s="5"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="54"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="49"/>
       <c r="E22" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="30">
-        <v>52.9</v>
-      </c>
-      <c r="G22" s="30">
-        <v>52.9</v>
-      </c>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="30">
         <v>47.59</v>
       </c>
-      <c r="I22" s="47"/>
+      <c r="I22" s="51"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -1768,27 +1737,27 @@
       <c r="N22" s="5"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="50" t="s">
+      <c r="A23" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="B23" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="40">
         <v>1</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="23"/>
-      <c r="I23" s="38">
+      <c r="I23" s="42">
         <f>AVERAGE(F24:H24)</f>
         <v>13.89</v>
       </c>
@@ -1799,10 +1768,10 @@
       <c r="N23" s="5"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="53"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="24" t="s">
         <v>17</v>
       </c>
@@ -1811,7 +1780,7 @@
       </c>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
-      <c r="I24" s="39"/>
+      <c r="I24" s="43"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -1819,27 +1788,27 @@
       <c r="N24" s="5"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="42" t="s">
+      <c r="A25" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="48">
         <v>1</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="46">
+      <c r="I25" s="50">
         <f>AVERAGE(F26:H26)</f>
         <v>5.89</v>
       </c>
@@ -1850,10 +1819,10 @@
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="56"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="49"/>
       <c r="E26" s="29" t="s">
         <v>17</v>
       </c>
@@ -1862,7 +1831,7 @@
       </c>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
-      <c r="I26" s="47"/>
+      <c r="I26" s="51"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -1870,27 +1839,27 @@
       <c r="N26" s="5"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="34" t="s">
+      <c r="A27" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="59">
         <v>1</v>
       </c>
       <c r="E27" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G27" s="22"/>
       <c r="H27" s="23"/>
-      <c r="I27" s="38">
+      <c r="I27" s="42">
         <f>AVERAGE(F28:H28)</f>
         <v>8.49</v>
       </c>
@@ -1901,10 +1870,10 @@
       <c r="N27" s="5"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="37"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="60"/>
       <c r="E28" s="24" t="s">
         <v>17</v>
       </c>
@@ -1913,7 +1882,7 @@
       </c>
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
-      <c r="I28" s="39"/>
+      <c r="I28" s="43"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -1921,33 +1890,31 @@
       <c r="N28" s="5"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="44">
+      <c r="A29" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="48">
         <v>1</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>58</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G29" s="27"/>
       <c r="H29" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="46">
+        <v>36</v>
+      </c>
+      <c r="I29" s="50">
         <f>AVERAGE(F30:H30)</f>
-        <v>5.3866666666666667</v>
+        <v>5.1850000000000005</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -1956,23 +1923,21 @@
       <c r="N29" s="5"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="41"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="45"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="54"/>
       <c r="E30" s="24" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="30">
         <v>4.99</v>
       </c>
-      <c r="G30" s="30">
-        <v>5.79</v>
-      </c>
+      <c r="G30" s="30"/>
       <c r="H30" s="30">
         <v>5.38</v>
       </c>
-      <c r="I30" s="47"/>
+      <c r="I30" s="51"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
@@ -1980,27 +1945,27 @@
       <c r="N30" s="5"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="34" t="s">
+      <c r="A31" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="59">
         <v>1</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G31" s="22"/>
       <c r="H31" s="23"/>
-      <c r="I31" s="38">
+      <c r="I31" s="42">
         <f>AVERAGE(F32:H32)</f>
         <v>4.99</v>
       </c>
@@ -2011,10 +1976,10 @@
       <c r="N31" s="5"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="37"/>
+      <c r="A32" s="56"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="60"/>
       <c r="E32" s="24" t="s">
         <v>17</v>
       </c>
@@ -2023,7 +1988,7 @@
       </c>
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
-      <c r="I32" s="39"/>
+      <c r="I32" s="43"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
@@ -2048,6 +2013,67 @@
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="I9:I10"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:H6"/>
@@ -2055,67 +2081,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="I31:I32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
